--- a/Phase - 7 Automation Testing/TestNG/tutorialninja/src/test/resources/dataset.xlsx
+++ b/Phase - 7 Automation Testing/TestNG/tutorialninja/src/test/resources/dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EXPLEO SMARTCLIFF\Phase - 7 Automation Testing\TestNG\tutorialninja\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322DE6B7-2E2F-46A9-BA78-7DD8AC3E8F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E556685B-C284-4D81-87D8-E9DB82CAAF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>username</t>
   </si>
@@ -45,44 +45,29 @@
     <t>admin123</t>
   </si>
   <si>
-    <t>admin234</t>
-  </si>
-  <si>
-    <t>hl@gmail.com</t>
-  </si>
-  <si>
-    <t>vigneshwaran.coder@gmail.com</t>
-  </si>
-  <si>
     <t>Valid Search Keys</t>
   </si>
   <si>
-    <t>Mac</t>
-  </si>
-  <si>
-    <t>Apple</t>
-  </si>
-  <si>
-    <t>Samsung</t>
-  </si>
-  <si>
-    <t>Laptop</t>
-  </si>
-  <si>
-    <t>Mobile</t>
-  </si>
-  <si>
     <t>Invalid Search Keys</t>
   </si>
   <si>
-    <t>kiot</t>
+    <t>mac</t>
+  </si>
+  <si>
+    <t>hl@gmail.co</t>
+  </si>
+  <si>
+    <t>mac1</t>
+  </si>
+  <si>
+    <t>admin543</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,6 +77,13 @@
     </font>
     <font>
       <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
@@ -120,9 +112,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -420,32 +413,27 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
-        <v>1234</v>
-      </c>
+      <c r="A3" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{3885BFD3-9AF8-4077-85D5-D0FD9CB3313A}"/>
-    <hyperlink ref="A2" r:id="rId2" xr:uid="{2A6328EB-13B7-4FA0-BAE2-E07217A78FF3}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{2A6328EB-13B7-4FA0-BAE2-E07217A78FF3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00E49E09-5B52-4002-B3E4-79CC20826B38}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
@@ -467,14 +455,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -482,7 +462,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{047E1E29-C413-4A31-90CE-76B3388DA617}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -490,7 +470,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -498,16 +478,6 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -515,27 +485,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4890DDF5-6DBD-483B-832B-FB70E1B2204E}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Phase - 7 Automation Testing/TestNG/tutorialninja/src/test/resources/dataset.xlsx
+++ b/Phase - 7 Automation Testing/TestNG/tutorialninja/src/test/resources/dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EXPLEO SMARTCLIFF\Phase - 7 Automation Testing\TestNG\tutorialninja\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E556685B-C284-4D81-87D8-E9DB82CAAF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35B3C413-7FE1-4301-9553-039CCE553DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t>username</t>
   </si>
@@ -45,22 +46,19 @@
     <t>admin123</t>
   </si>
   <si>
+    <t>hl@gmail.com</t>
+  </si>
+  <si>
     <t>Valid Search Keys</t>
   </si>
   <si>
     <t>Invalid Search Keys</t>
   </si>
   <si>
+    <t>kiot</t>
+  </si>
+  <si>
     <t>mac</t>
-  </si>
-  <si>
-    <t>hl@gmail.co</t>
-  </si>
-  <si>
-    <t>mac1</t>
-  </si>
-  <si>
-    <t>admin543</t>
   </si>
 </sst>
 </file>
@@ -413,10 +411,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -470,7 +468,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -490,12 +488,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
